--- a/Result/profitability/4721.xlsx
+++ b/Result/profitability/4721.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.88</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8350000000000001</v>
+        <v>1.0125</v>
       </c>
       <c r="N2" t="n">
-        <v>18.9225</v>
+        <v>20.02375</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.74</v>
       </c>
       <c r="M3" t="n">
-        <v>0.87625</v>
+        <v>1.01625</v>
       </c>
       <c r="N3" t="n">
-        <v>18.13125</v>
+        <v>19.22375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8275</v>
+        <v>0.9625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.54</v>
+        <v>18.20375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7125</v>
+        <v>0.8412500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>15.8825</v>
+        <v>17.655</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.62375</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>16.16125</v>
+        <v>17.0775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0.58875</v>
+        <v>0.7037500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>15.755</v>
+        <v>15.88625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5175</v>
+        <v>0.5375</v>
       </c>
       <c r="N8" t="n">
-        <v>13.845</v>
+        <v>13.96625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4721</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>813</v>
+      </c>
+      <c r="D75" t="n">
+        <v>597</v>
+      </c>
+      <c r="E75" t="n">
+        <v>217</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>169</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>171</v>
+      </c>
+      <c r="K75" t="n">
+        <v>137</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9537500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.83125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09580838323353302</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9699999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03780202650038977</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.2875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.138955823293173</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
